--- a/output_data/charts/0500000US39045.xlsx
+++ b/output_data/charts/0500000US39045.xlsx
@@ -167,10 +167,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -212,16 +212,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$15</c:f>
+              <c:f>Sheet1!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.129719687448773</c:v>
                 </c:pt>
@@ -253,16 +256,19 @@
                   <c:v>1.928308275682771</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.134238121519241</c:v>
+                  <c:v>2.133396879546481</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.368974436911091</c:v>
+                  <c:v>2.367825358925858</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.862735953263458</c:v>
+                  <c:v>2.916048686613633</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.203313981615868</c:v>
+                  <c:v>3.328503290466703</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.835791180362657</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -292,10 +298,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -337,16 +343,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$15</c:f>
+              <c:f>Sheet1!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>5.991475875635211</c:v>
                 </c:pt>
@@ -378,16 +387,19 @@
                   <c:v>8.469718394703969</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>9.03680196678541</c:v>
+                  <c:v>9.036522349872071</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9.484582126308085</c:v>
+                  <c:v>9.484945269620763</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.993495176612091</c:v>
+                  <c:v>10.03517889756444</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>10.5218916303822</c:v>
+                  <c:v>10.54941737607921</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>10.99831904722166</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,10 +429,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -462,16 +474,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$15</c:f>
+              <c:f>Sheet1!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.722583465384405</c:v>
                 </c:pt>
@@ -503,16 +518,19 @@
                   <c:v>2.398178855189819</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.573252721890522</c:v>
+                  <c:v>2.572367430893493</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.67168706461798</c:v>
+                  <c:v>2.670470402183013</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.754117675937063</c:v>
+                  <c:v>2.746895799369967</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.867077890662797</c:v>
+                  <c:v>2.853951578820262</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.936302619186705</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -542,10 +560,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -587,16 +605,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$15</c:f>
+              <c:f>Sheet1!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.2178842686192012</c:v>
                 </c:pt>
@@ -628,16 +649,19 @@
                   <c:v>0.2320818246957889</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2257789373338016</c:v>
+                  <c:v>0.224502081974615</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.225173532495084</c:v>
+                  <c:v>0.223262736829049</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2184638798203196</c:v>
+                  <c:v>0.2169569640733977</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.2189163038219642</c:v>
+                  <c:v>0.2179556843566987</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.2348565229312955</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -667,10 +691,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -712,16 +736,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$15</c:f>
+              <c:f>Sheet1!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.719851374241845</c:v>
                 </c:pt>
@@ -753,16 +780,19 @@
                   <c:v>2.109027729339328</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.166850634689679</c:v>
+                  <c:v>2.167887422866603</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.186602484972923</c:v>
+                  <c:v>2.18797482092468</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.332531480890547</c:v>
+                  <c:v>2.336271036858169</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.434687953555878</c:v>
+                  <c:v>2.443397935156675</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.561366698060347</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -792,10 +822,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -837,16 +867,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$15</c:f>
+              <c:f>Sheet1!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>89.21848532867057</c:v>
                 </c:pt>
@@ -878,16 +911,19 @@
                   <c:v>84.86268492038832</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>83.86307761778134</c:v>
+                  <c:v>83.86532383484673</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>83.06298035469484</c:v>
+                  <c:v>83.06552141151664</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>81.83865583347652</c:v>
+                  <c:v>81.74864861552039</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>80.7541122399613</c:v>
+                  <c:v>80.60677413512045</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>79.43336393223733</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,13 +1042,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1428750</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1320,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" customWidth="1"/>
@@ -1590,22 +1626,22 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2">
-        <v>2.134238121519241</v>
+        <v>2.133396879546481</v>
       </c>
       <c r="C12" s="2">
-        <v>9.03680196678541</v>
+        <v>9.036522349872071</v>
       </c>
       <c r="D12" s="2">
-        <v>2.573252721890522</v>
+        <v>2.572367430893493</v>
       </c>
       <c r="E12" s="2">
-        <v>0.2257789373338016</v>
+        <v>0.224502081974615</v>
       </c>
       <c r="F12" s="2">
-        <v>2.166850634689679</v>
+        <v>2.167887422866603</v>
       </c>
       <c r="G12" s="2">
-        <v>83.86307761778134</v>
+        <v>83.86532383484673</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1613,22 +1649,22 @@
         <v>2021</v>
       </c>
       <c r="B13" s="2">
-        <v>2.368974436911091</v>
+        <v>2.367825358925858</v>
       </c>
       <c r="C13" s="2">
-        <v>9.484582126308085</v>
+        <v>9.484945269620763</v>
       </c>
       <c r="D13" s="2">
-        <v>2.67168706461798</v>
+        <v>2.670470402183013</v>
       </c>
       <c r="E13" s="2">
-        <v>0.225173532495084</v>
+        <v>0.223262736829049</v>
       </c>
       <c r="F13" s="2">
-        <v>2.186602484972923</v>
+        <v>2.18797482092468</v>
       </c>
       <c r="G13" s="2">
-        <v>83.06298035469484</v>
+        <v>83.06552141151664</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1636,22 +1672,22 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2">
-        <v>2.862735953263458</v>
+        <v>2.916048686613633</v>
       </c>
       <c r="C14" s="2">
-        <v>9.993495176612091</v>
+        <v>10.03517889756444</v>
       </c>
       <c r="D14" s="2">
-        <v>2.754117675937063</v>
+        <v>2.746895799369967</v>
       </c>
       <c r="E14" s="2">
-        <v>0.2184638798203196</v>
+        <v>0.2169569640733977</v>
       </c>
       <c r="F14" s="2">
-        <v>2.332531480890547</v>
+        <v>2.336271036858169</v>
       </c>
       <c r="G14" s="2">
-        <v>81.83865583347652</v>
+        <v>81.74864861552039</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1659,22 +1695,45 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>3.203313981615868</v>
+        <v>3.328503290466703</v>
       </c>
       <c r="C15" s="2">
-        <v>10.5218916303822</v>
+        <v>10.54941737607921</v>
       </c>
       <c r="D15" s="2">
-        <v>2.867077890662797</v>
+        <v>2.853951578820262</v>
       </c>
       <c r="E15" s="2">
-        <v>0.2189163038219642</v>
+        <v>0.2179556843566987</v>
       </c>
       <c r="F15" s="2">
-        <v>2.434687953555878</v>
+        <v>2.443397935156675</v>
       </c>
       <c r="G15" s="2">
-        <v>80.7541122399613</v>
+        <v>80.60677413512045</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3.835791180362657</v>
+      </c>
+      <c r="C16" s="2">
+        <v>10.99831904722166</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2.936302619186705</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.2348565229312955</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2.561366698060347</v>
+      </c>
+      <c r="G16" s="2">
+        <v>79.43336393223733</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39045.xlsx
+++ b/output_data/charts/0500000US39045.xlsx
@@ -226,34 +226,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.129719687448773</c:v>
+                  <c:v>1.129650245531598</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.167957602935181</c:v>
+                  <c:v>1.168005218313017</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.194726909866</c:v>
+                  <c:v>1.192116822017502</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.250503964520898</c:v>
+                  <c:v>1.246001236592382</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.268617021276596</c:v>
+                  <c:v>1.262303804203246</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.314519859890292</c:v>
+                  <c:v>1.308395149880334</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.442134673393139</c:v>
+                  <c:v>1.421568306618932</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.589989529337246</c:v>
+                  <c:v>1.570924324114658</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.766605579833656</c:v>
+                  <c:v>1.757895141747125</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.928308275682771</c:v>
+                  <c:v>1.904502011753208</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.133396879546481</c:v>
@@ -357,34 +357,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>5.991475875635211</c:v>
+                  <c:v>5.991107589965647</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.17543144448974</c:v>
+                  <c:v>6.172965333550763</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.382285458272804</c:v>
+                  <c:v>6.38284872472013</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.752452627335035</c:v>
+                  <c:v>6.756230006182962</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.027260638297872</c:v>
+                  <c:v>7.028465017291833</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.144273346110634</c:v>
+                  <c:v>7.145596149523318</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.469786493401122</c:v>
+                  <c:v>7.488104510141437</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.836192298245841</c:v>
+                  <c:v>7.859793387895479</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.036549576450385</c:v>
+                  <c:v>8.079778435973381</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.469718394703969</c:v>
+                  <c:v>8.481729219287445</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>9.036522349872071</c:v>
@@ -488,34 +488,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.722583465384405</c:v>
+                  <c:v>1.722477581155194</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.786927571680935</c:v>
+                  <c:v>1.782923614225339</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.848432599752909</c:v>
+                  <c:v>1.844522440445075</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.900282220131703</c:v>
+                  <c:v>1.891851931503535</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.005984042553191</c:v>
+                  <c:v>1.995211492418196</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.044808670940453</c:v>
+                  <c:v>2.02903724860169</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.131140032323708</c:v>
+                  <c:v>2.119262512353638</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.202070864411381</c:v>
+                  <c:v>2.18248580996341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.306775512296395</c:v>
+                  <c:v>2.287443422959059</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.398178855189819</c:v>
+                  <c:v>2.374122634444769</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.572367430893493</c:v>
@@ -619,34 +619,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.2178842686192012</c:v>
+                  <c:v>0.2185538564510952</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2282918874847126</c:v>
+                  <c:v>0.2303395980268254</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2328359830022944</c:v>
+                  <c:v>0.2355720599317045</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2392151592527886</c:v>
+                  <c:v>0.2426140487647517</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2393617021276596</c:v>
+                  <c:v>0.2427507315775472</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2339567774767035</c:v>
+                  <c:v>0.2393325135203036</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2335944094379993</c:v>
+                  <c:v>0.2395460406181074</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2430227898499205</c:v>
+                  <c:v>0.2495377732955794</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2325998641565532</c:v>
+                  <c:v>0.237206857201472</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2320818246957889</c:v>
+                  <c:v>0.2379834236612639</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.224502081974615</c:v>
@@ -750,34 +750,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.719851374241845</c:v>
+                  <c:v>1.720428638750965</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.74004620192961</c:v>
+                  <c:v>1.737399268892603</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.760185725728715</c:v>
+                  <c:v>1.752194486120257</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.794785647090445</c:v>
+                  <c:v>1.782305975967096</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.836436170212766</c:v>
+                  <c:v>1.82096302208034</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.87760227347829</c:v>
+                  <c:v>1.857802107712854</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.930261926728566</c:v>
+                  <c:v>1.900660387855147</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.949353016455745</c:v>
+                  <c:v>1.914846851040171</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.055593289846343</c:v>
+                  <c:v>2.011129489300048</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.109027729339328</c:v>
+                  <c:v>2.066965362305964</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.167887422866603</c:v>
@@ -881,34 +881,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>89.21848532867057</c:v>
+                  <c:v>89.2177820881455</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>88.90134529147981</c:v>
+                  <c:v>88.90836696699145</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>88.58153332337727</c:v>
+                  <c:v>88.59274546676534</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>88.06276038166912</c:v>
+                  <c:v>88.08099680098927</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>87.62234042553192</c:v>
+                  <c:v>87.65030593242884</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>87.38483907210363</c:v>
+                  <c:v>87.4198368307615</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>86.79308246471547</c:v>
+                  <c:v>86.83085824241273</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>86.17937150169986</c:v>
+                  <c:v>86.2224118536907</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>85.60187617741667</c:v>
+                  <c:v>85.62654665281892</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>84.86268492038832</c:v>
+                  <c:v>84.93469734854735</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>83.86532383484673</c:v>
@@ -1396,22 +1396,22 @@
         <v>2010</v>
       </c>
       <c r="B2" s="2">
-        <v>1.129719687448773</v>
+        <v>1.129650245531598</v>
       </c>
       <c r="C2" s="2">
-        <v>5.991475875635211</v>
+        <v>5.991107589965647</v>
       </c>
       <c r="D2" s="2">
-        <v>1.722583465384405</v>
+        <v>1.722477581155194</v>
       </c>
       <c r="E2" s="2">
-        <v>0.2178842686192012</v>
+        <v>0.2185538564510952</v>
       </c>
       <c r="F2" s="2">
-        <v>1.719851374241845</v>
+        <v>1.720428638750965</v>
       </c>
       <c r="G2" s="2">
-        <v>89.21848532867057</v>
+        <v>89.2177820881455</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1419,22 +1419,22 @@
         <v>2011</v>
       </c>
       <c r="B3" s="2">
-        <v>1.167957602935181</v>
+        <v>1.168005218313017</v>
       </c>
       <c r="C3" s="2">
-        <v>6.17543144448974</v>
+        <v>6.172965333550763</v>
       </c>
       <c r="D3" s="2">
-        <v>1.786927571680935</v>
+        <v>1.782923614225339</v>
       </c>
       <c r="E3" s="2">
-        <v>0.2282918874847126</v>
+        <v>0.2303395980268254</v>
       </c>
       <c r="F3" s="2">
-        <v>1.74004620192961</v>
+        <v>1.737399268892603</v>
       </c>
       <c r="G3" s="2">
-        <v>88.90134529147981</v>
+        <v>88.90836696699145</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1442,22 +1442,22 @@
         <v>2012</v>
       </c>
       <c r="B4" s="2">
-        <v>1.194726909866</v>
+        <v>1.192116822017502</v>
       </c>
       <c r="C4" s="2">
-        <v>6.382285458272804</v>
+        <v>6.38284872472013</v>
       </c>
       <c r="D4" s="2">
-        <v>1.848432599752909</v>
+        <v>1.844522440445075</v>
       </c>
       <c r="E4" s="2">
-        <v>0.2328359830022944</v>
+        <v>0.2355720599317045</v>
       </c>
       <c r="F4" s="2">
-        <v>1.760185725728715</v>
+        <v>1.752194486120257</v>
       </c>
       <c r="G4" s="2">
-        <v>88.58153332337727</v>
+        <v>88.59274546676534</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1465,22 +1465,22 @@
         <v>2013</v>
       </c>
       <c r="B5" s="2">
-        <v>1.250503964520898</v>
+        <v>1.246001236592382</v>
       </c>
       <c r="C5" s="2">
-        <v>6.752452627335035</v>
+        <v>6.756230006182962</v>
       </c>
       <c r="D5" s="2">
-        <v>1.900282220131703</v>
+        <v>1.891851931503535</v>
       </c>
       <c r="E5" s="2">
-        <v>0.2392151592527886</v>
+        <v>0.2426140487647517</v>
       </c>
       <c r="F5" s="2">
-        <v>1.794785647090445</v>
+        <v>1.782305975967096</v>
       </c>
       <c r="G5" s="2">
-        <v>88.06276038166912</v>
+        <v>88.08099680098927</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1488,22 +1488,22 @@
         <v>2014</v>
       </c>
       <c r="B6" s="2">
-        <v>1.268617021276596</v>
+        <v>1.262303804203246</v>
       </c>
       <c r="C6" s="2">
-        <v>7.027260638297872</v>
+        <v>7.028465017291833</v>
       </c>
       <c r="D6" s="2">
-        <v>2.005984042553191</v>
+        <v>1.995211492418196</v>
       </c>
       <c r="E6" s="2">
-        <v>0.2393617021276596</v>
+        <v>0.2427507315775472</v>
       </c>
       <c r="F6" s="2">
-        <v>1.836436170212766</v>
+        <v>1.82096302208034</v>
       </c>
       <c r="G6" s="2">
-        <v>87.62234042553192</v>
+        <v>87.65030593242884</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1511,22 +1511,22 @@
         <v>2015</v>
       </c>
       <c r="B7" s="2">
-        <v>1.314519859890292</v>
+        <v>1.308395149880334</v>
       </c>
       <c r="C7" s="2">
-        <v>7.144273346110634</v>
+        <v>7.145596149523318</v>
       </c>
       <c r="D7" s="2">
-        <v>2.044808670940453</v>
+        <v>2.02903724860169</v>
       </c>
       <c r="E7" s="2">
-        <v>0.2339567774767035</v>
+        <v>0.2393325135203036</v>
       </c>
       <c r="F7" s="2">
-        <v>1.87760227347829</v>
+        <v>1.857802107712854</v>
       </c>
       <c r="G7" s="2">
-        <v>87.38483907210363</v>
+        <v>87.4198368307615</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1534,22 +1534,22 @@
         <v>2016</v>
       </c>
       <c r="B8" s="2">
-        <v>1.442134673393139</v>
+        <v>1.421568306618932</v>
       </c>
       <c r="C8" s="2">
-        <v>7.469786493401122</v>
+        <v>7.488104510141437</v>
       </c>
       <c r="D8" s="2">
-        <v>2.131140032323708</v>
+        <v>2.119262512353638</v>
       </c>
       <c r="E8" s="2">
-        <v>0.2335944094379993</v>
+        <v>0.2395460406181074</v>
       </c>
       <c r="F8" s="2">
-        <v>1.930261926728566</v>
+        <v>1.900660387855147</v>
       </c>
       <c r="G8" s="2">
-        <v>86.79308246471547</v>
+        <v>86.83085824241273</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1557,22 +1557,22 @@
         <v>2017</v>
       </c>
       <c r="B9" s="2">
-        <v>1.589989529337246</v>
+        <v>1.570924324114658</v>
       </c>
       <c r="C9" s="2">
-        <v>7.836192298245841</v>
+        <v>7.859793387895479</v>
       </c>
       <c r="D9" s="2">
-        <v>2.202070864411381</v>
+        <v>2.18248580996341</v>
       </c>
       <c r="E9" s="2">
-        <v>0.2430227898499205</v>
+        <v>0.2495377732955794</v>
       </c>
       <c r="F9" s="2">
-        <v>1.949353016455745</v>
+        <v>1.914846851040171</v>
       </c>
       <c r="G9" s="2">
-        <v>86.17937150169986</v>
+        <v>86.2224118536907</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1580,22 +1580,22 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2">
-        <v>1.766605579833656</v>
+        <v>1.757895141747125</v>
       </c>
       <c r="C10" s="2">
-        <v>8.036549576450385</v>
+        <v>8.079778435973381</v>
       </c>
       <c r="D10" s="2">
-        <v>2.306775512296395</v>
+        <v>2.287443422959059</v>
       </c>
       <c r="E10" s="2">
-        <v>0.2325998641565532</v>
+        <v>0.237206857201472</v>
       </c>
       <c r="F10" s="2">
-        <v>2.055593289846343</v>
+        <v>2.011129489300048</v>
       </c>
       <c r="G10" s="2">
-        <v>85.60187617741667</v>
+        <v>85.62654665281892</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1603,22 +1603,22 @@
         <v>2019</v>
       </c>
       <c r="B11" s="2">
-        <v>1.928308275682771</v>
+        <v>1.904502011753208</v>
       </c>
       <c r="C11" s="2">
-        <v>8.469718394703969</v>
+        <v>8.481729219287445</v>
       </c>
       <c r="D11" s="2">
-        <v>2.398178855189819</v>
+        <v>2.374122634444769</v>
       </c>
       <c r="E11" s="2">
-        <v>0.2320818246957889</v>
+        <v>0.2379834236612639</v>
       </c>
       <c r="F11" s="2">
-        <v>2.109027729339328</v>
+        <v>2.066965362305964</v>
       </c>
       <c r="G11" s="2">
-        <v>84.86268492038832</v>
+        <v>84.93469734854735</v>
       </c>
     </row>
     <row r="12" spans="1:7">
